--- a/docs/downloads/13/tbl_codes_aberrants_marovoay_maroala.xlsx
+++ b/docs/downloads/13/tbl_codes_aberrants_marovoay_maroala.xlsx
@@ -351,13 +351,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G28"/>
+  <dimension ref="A1:E28"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>j5</t>
+          <t>Obs_n</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -367,25 +367,15 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Enqueteur</t>
+          <t>j11</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Hameau</t>
+          <t>qual1aa</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>j11</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>qual1aa</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>qual2aa</t>
         </is>
@@ -393,7 +383,7 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>311102</v>
+        <v>1</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -402,29 +392,19 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>E19</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Ampijoroa Andolobe</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Mauvaise</t>
-        </is>
-      </c>
-      <c r="F2">
-        <v>3</v>
-      </c>
-      <c r="G2">
+          <t>Mauvaise</t>
+        </is>
+      </c>
+      <c r="D2">
+        <v>3</v>
+      </c>
+      <c r="E2">
         <v>3</v>
       </c>
     </row>
     <row r="3">
       <c r="A3">
-        <v>310316</v>
+        <v>2</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -433,29 +413,19 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>E12</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Ampijoroa Morafeno</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Mauvaise</t>
-        </is>
-      </c>
-      <c r="F3">
-        <v>3</v>
-      </c>
-      <c r="G3">
+          <t>Mauvaise</t>
+        </is>
+      </c>
+      <c r="D3">
+        <v>3</v>
+      </c>
+      <c r="E3">
         <v>1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4">
-        <v>310318</v>
+        <v>3</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -464,29 +434,19 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>E13</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Ampijoroa Morafeno</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Mauvaise</t>
-        </is>
-      </c>
-      <c r="F4">
-        <v>3</v>
-      </c>
-      <c r="G4">
+          <t>Mauvaise</t>
+        </is>
+      </c>
+      <c r="D4">
+        <v>3</v>
+      </c>
+      <c r="E4">
         <v>3</v>
       </c>
     </row>
     <row r="5">
       <c r="A5">
-        <v>310121</v>
+        <v>4</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -495,29 +455,19 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>E11</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Ampijoroa Ambalakida</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
           <t>Moyenne</t>
         </is>
       </c>
-      <c r="F5">
-        <v>3</v>
-      </c>
-      <c r="G5">
+      <c r="D5">
+        <v>3</v>
+      </c>
+      <c r="E5">
         <v>2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6">
-        <v>310813</v>
+        <v>5</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -526,29 +476,19 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>E14</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Maroala Soamandroso</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Mauvaise</t>
-        </is>
-      </c>
-      <c r="F6">
-        <v>3</v>
-      </c>
-      <c r="G6">
+          <t>Mauvaise</t>
+        </is>
+      </c>
+      <c r="D6">
+        <v>3</v>
+      </c>
+      <c r="E6">
         <v>3</v>
       </c>
     </row>
     <row r="7">
       <c r="A7">
-        <v>310508</v>
+        <v>6</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -557,29 +497,19 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>E12</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Maroala Ambomiray</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Mauvaise</t>
-        </is>
-      </c>
-      <c r="F7">
-        <v>3</v>
-      </c>
-      <c r="G7">
+          <t>Mauvaise</t>
+        </is>
+      </c>
+      <c r="D7">
+        <v>3</v>
+      </c>
+      <c r="E7">
         <v>1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8">
-        <v>310809</v>
+        <v>7</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -588,29 +518,19 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>E11</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Maroala Soamandroso</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
           <t>Moyenne</t>
         </is>
       </c>
-      <c r="F8">
-        <v>3</v>
-      </c>
-      <c r="G8">
+      <c r="D8">
+        <v>3</v>
+      </c>
+      <c r="E8">
         <v>1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9">
-        <v>310921</v>
+        <v>8</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -619,29 +539,19 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>E12</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Maroala Morafeno</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Mauvaise</t>
-        </is>
-      </c>
-      <c r="F9">
-        <v>3</v>
-      </c>
-      <c r="G9">
+          <t>Mauvaise</t>
+        </is>
+      </c>
+      <c r="D9">
+        <v>3</v>
+      </c>
+      <c r="E9">
         <v>2</v>
       </c>
     </row>
     <row r="10">
       <c r="A10">
-        <v>310407</v>
+        <v>9</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -650,29 +560,19 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>E19</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Maroala Antanandava</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
           <t>Moyenne</t>
         </is>
       </c>
-      <c r="F10">
-        <v>3</v>
-      </c>
-      <c r="G10">
+      <c r="D10">
+        <v>3</v>
+      </c>
+      <c r="E10">
         <v>3</v>
       </c>
     </row>
     <row r="11">
       <c r="A11">
-        <v>310426</v>
+        <v>10</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -681,29 +581,19 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>E12</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Maroala Antanandava</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Mauvaise</t>
-        </is>
-      </c>
-      <c r="F11">
-        <v>3</v>
-      </c>
-      <c r="G11">
+          <t>Mauvaise</t>
+        </is>
+      </c>
+      <c r="D11">
+        <v>3</v>
+      </c>
+      <c r="E11">
         <v>1</v>
       </c>
     </row>
     <row r="12">
       <c r="A12">
-        <v>310801</v>
+        <v>11</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -712,29 +602,19 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>E12</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Maroala Soamandroso</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Mauvaise</t>
-        </is>
-      </c>
-      <c r="F12">
-        <v>3</v>
-      </c>
-      <c r="G12">
+          <t>Mauvaise</t>
+        </is>
+      </c>
+      <c r="D12">
+        <v>3</v>
+      </c>
+      <c r="E12">
         <v>1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13">
-        <v>330125</v>
+        <v>12</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -743,29 +623,19 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>E14</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Madiromiongana</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
           <t>Moyenne</t>
         </is>
       </c>
-      <c r="F13">
-        <v>3</v>
-      </c>
-      <c r="G13">
+      <c r="D13">
+        <v>3</v>
+      </c>
+      <c r="E13">
         <v>3</v>
       </c>
     </row>
     <row r="14">
       <c r="A14">
-        <v>330614</v>
+        <v>13</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -774,29 +644,19 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>E13</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Madiromiongana Tsaratanteraka</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Mauvaise</t>
-        </is>
-      </c>
-      <c r="F14">
-        <v>3</v>
-      </c>
-      <c r="G14">
+          <t>Mauvaise</t>
+        </is>
+      </c>
+      <c r="D14">
+        <v>3</v>
+      </c>
+      <c r="E14">
         <v>3</v>
       </c>
     </row>
     <row r="15">
       <c r="A15">
-        <v>320530</v>
+        <v>14</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -805,29 +665,19 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>E11</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Bepako Avara-dalana</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
           <t>Moyenne</t>
         </is>
       </c>
-      <c r="F15">
-        <v>3</v>
-      </c>
-      <c r="G15">
+      <c r="D15">
+        <v>3</v>
+      </c>
+      <c r="E15">
         <v>1</v>
       </c>
     </row>
     <row r="16">
       <c r="A16">
-        <v>320406</v>
+        <v>15</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -836,29 +686,19 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>E14</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Bepako Atsimon-dalana</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Mauvaise</t>
-        </is>
-      </c>
-      <c r="F16">
-        <v>3</v>
-      </c>
-      <c r="G16">
+          <t>Mauvaise</t>
+        </is>
+      </c>
+      <c r="D16">
+        <v>3</v>
+      </c>
+      <c r="E16">
         <v>3</v>
       </c>
     </row>
     <row r="17">
       <c r="A17">
-        <v>320413</v>
+        <v>16</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -866,16 +706,6 @@
         </is>
       </c>
       <c r="C17" t="inlineStr">
-        <is>
-          <t>E12</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Bepako Atsimon-dalana</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
         <is>
           <t>Bonne</t>
         </is>
@@ -883,7 +713,7 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>330304</v>
+        <v>17</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -892,29 +722,19 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>E11</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Madiromiongana Ambonara II</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>Mauvaise</t>
-        </is>
-      </c>
-      <c r="F18">
-        <v>3</v>
-      </c>
-      <c r="G18">
+          <t>Mauvaise</t>
+        </is>
+      </c>
+      <c r="D18">
+        <v>3</v>
+      </c>
+      <c r="E18">
         <v>1</v>
       </c>
     </row>
     <row r="19">
       <c r="A19">
-        <v>320113</v>
+        <v>18</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -922,16 +742,6 @@
         </is>
       </c>
       <c r="C19" t="inlineStr">
-        <is>
-          <t>E17</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Bepako Ambany atsimo</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
         <is>
           <t>Moyenne</t>
         </is>
@@ -939,7 +749,7 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>320324</v>
+        <v>19</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -948,29 +758,19 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>E17</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Bepako Ambony atsinanana</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>Mauvaise</t>
-        </is>
-      </c>
-      <c r="F20">
-        <v>3</v>
-      </c>
-      <c r="G20">
+          <t>Mauvaise</t>
+        </is>
+      </c>
+      <c r="D20">
+        <v>3</v>
+      </c>
+      <c r="E20">
         <v>2</v>
       </c>
     </row>
     <row r="21">
       <c r="A21">
-        <v>320405</v>
+        <v>20</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -979,29 +779,19 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>E14</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Bepako Atsimon-dalana</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
           <t>Moyenne</t>
         </is>
       </c>
-      <c r="F21">
-        <v>3</v>
-      </c>
-      <c r="G21">
+      <c r="D21">
+        <v>3</v>
+      </c>
+      <c r="E21">
         <v>3</v>
       </c>
     </row>
     <row r="22">
       <c r="A22">
-        <v>310813</v>
+        <v>21</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -1010,29 +800,19 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>E14</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Maroala Soamandroso</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>Mauvaise</t>
-        </is>
-      </c>
-      <c r="F22">
-        <v>3</v>
-      </c>
-      <c r="G22">
+          <t>Mauvaise</t>
+        </is>
+      </c>
+      <c r="D22">
+        <v>3</v>
+      </c>
+      <c r="E22">
         <v>3</v>
       </c>
     </row>
     <row r="23">
       <c r="A23">
-        <v>310508</v>
+        <v>22</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -1041,29 +821,19 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>E12</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Maroala Ambomiray</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>Mauvaise</t>
-        </is>
-      </c>
-      <c r="F23">
-        <v>3</v>
-      </c>
-      <c r="G23">
+          <t>Mauvaise</t>
+        </is>
+      </c>
+      <c r="D23">
+        <v>3</v>
+      </c>
+      <c r="E23">
         <v>1</v>
       </c>
     </row>
     <row r="24">
       <c r="A24">
-        <v>310809</v>
+        <v>23</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -1072,29 +842,19 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>E11</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Maroala Soamandroso</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
           <t>Moyenne</t>
         </is>
       </c>
-      <c r="F24">
-        <v>3</v>
-      </c>
-      <c r="G24">
+      <c r="D24">
+        <v>3</v>
+      </c>
+      <c r="E24">
         <v>1</v>
       </c>
     </row>
     <row r="25">
       <c r="A25">
-        <v>310921</v>
+        <v>24</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -1103,29 +863,19 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>E12</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Maroala Morafeno</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>Mauvaise</t>
-        </is>
-      </c>
-      <c r="F25">
-        <v>3</v>
-      </c>
-      <c r="G25">
+          <t>Mauvaise</t>
+        </is>
+      </c>
+      <c r="D25">
+        <v>3</v>
+      </c>
+      <c r="E25">
         <v>2</v>
       </c>
     </row>
     <row r="26">
       <c r="A26">
-        <v>310407</v>
+        <v>25</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -1134,29 +884,19 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>E19</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Maroala Antanandava</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
           <t>Moyenne</t>
         </is>
       </c>
-      <c r="F26">
-        <v>3</v>
-      </c>
-      <c r="G26">
+      <c r="D26">
+        <v>3</v>
+      </c>
+      <c r="E26">
         <v>3</v>
       </c>
     </row>
     <row r="27">
       <c r="A27">
-        <v>310426</v>
+        <v>26</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -1165,29 +905,19 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>E12</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>Maroala Antanandava</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>Mauvaise</t>
-        </is>
-      </c>
-      <c r="F27">
-        <v>3</v>
-      </c>
-      <c r="G27">
+          <t>Mauvaise</t>
+        </is>
+      </c>
+      <c r="D27">
+        <v>3</v>
+      </c>
+      <c r="E27">
         <v>1</v>
       </c>
     </row>
     <row r="28">
       <c r="A28">
-        <v>310801</v>
+        <v>27</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
@@ -1196,23 +926,13 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>E12</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>Maroala Soamandroso</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>Mauvaise</t>
-        </is>
-      </c>
-      <c r="F28">
-        <v>3</v>
-      </c>
-      <c r="G28">
+          <t>Mauvaise</t>
+        </is>
+      </c>
+      <c r="D28">
+        <v>3</v>
+      </c>
+      <c r="E28">
         <v>1</v>
       </c>
     </row>
